--- a/entry/src/main/resources/rawfile/onlyoffice/templates/empty.xlsx
+++ b/entry/src/main/resources/rawfile/onlyoffice/templates/empty.xlsx
@@ -23,7 +23,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -109,13 +109,13 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Arial"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="SimSun"/>
         <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="SimSun"/>
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
